--- a/output/pdf_financials_xlsx/TSAT.xlsx
+++ b/output/pdf_financials_xlsx/TSAT.xlsx
@@ -3297,13 +3297,13 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>75.44799999999999</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>22.804</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>78.60899999999999</v>
       </c>
       <c r="F92" s="1" t="inlineStr">
         <is>
@@ -15732,7 +15732,11 @@
           <t>Reserves .�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
@@ -18196,7 +18200,11 @@
           <t>Reserves .�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -20305,7 +20313,11 @@
           <t>Reserves �������������������������������������������������������������������������������������������</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TSAT.xlsx
+++ b/output/pdf_financials_xlsx/TSAT.xlsx
@@ -4211,16 +4211,16 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-7486.93</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-453.592</v>
       </c>
       <c r="D124" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-97.23399999999999</v>
       </c>
       <c r="F124" s="3" t="n">
         <v>0</v>
@@ -4239,16 +4239,16 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-7486.93</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-453.592</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-97.23399999999999</v>
       </c>
       <c r="F125" s="3" t="n">
         <v>0</v>
@@ -29406,7 +29406,11 @@
           <t>Repayment of indebtedness .�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.� 33</t>
         </is>
       </c>
-      <c r="D501" t="inlineStr"/>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E501" t="inlineStr">
         <is>
           <t>-</t>
@@ -31223,7 +31227,11 @@
           <t>Repayment of indebtedness .�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.� 33</t>
         </is>
       </c>
-      <c r="D538" t="inlineStr"/>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E538" s="5" t="n">
         <v>-3743.465</v>
       </c>
@@ -33189,7 +33197,11 @@
           <t>Repayment of indebtedness ��������������������������������������������������������� 32</t>
         </is>
       </c>
-      <c r="D578" t="inlineStr"/>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E578" s="5" t="n">
         <v>-3743.465</v>
       </c>
@@ -34165,7 +34177,7 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
@@ -34849,7 +34861,7 @@
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
@@ -35290,7 +35302,7 @@
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
@@ -35719,7 +35731,11 @@
           <t>Operating expenses .�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.� 7﻿</t>
         </is>
       </c>
-      <c r="D630" t="inlineStr"/>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E630" t="inlineStr">
         <is>
           <t>-</t>
@@ -35731,13 +35747,13 @@
         </is>
       </c>
       <c r="G630" s="5" t="n">
-        <v>-236.949</v>
+        <v>236.949</v>
       </c>
       <c r="H630" s="5" t="n">
-        <v>-258.989</v>
+        <v>258.989</v>
       </c>
       <c r="I630" s="5" t="n">
-        <v>-204.552</v>
+        <v>204.552</v>
       </c>
       <c r="J630" t="inlineStr">
         <is>
@@ -35860,7 +35876,11 @@
           <t>Interest expense .�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.� 9﻿</t>
         </is>
       </c>
-      <c r="D633" t="inlineStr"/>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E633" t="inlineStr">
         <is>
           <t>-</t>
@@ -36524,7 +36544,7 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
@@ -37486,7 +37506,7 @@
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E667" s="5" t="n">
@@ -38525,7 +38545,7 @@
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E688" s="5" t="n">

--- a/output/pdf_financials_xlsx/TSAT.xlsx
+++ b/output/pdf_financials_xlsx/TSAT.xlsx
@@ -3506,13 +3506,13 @@
         <v>187.198</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>245.578</v>
+        <v>244.82</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>157.762</v>
+        <v>155.025</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>-81.59699999999999</v>
+        <v>-80.117</v>
       </c>
       <c r="F99" s="3" t="n">
         <v>583.27</v>
@@ -3979,22 +3979,22 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>0</v>
+        <v>-27.597</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-1.162</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-13.267</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.052</v>
       </c>
       <c r="H116" s="3" t="n">
         <v>0</v>
@@ -25050,7 +25050,11 @@
           <t>Purchase of intangible assets �.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�</t>
         </is>
       </c>
-      <c r="D411" t="inlineStr"/>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E411" t="inlineStr">
         <is>
           <t>-</t>
@@ -28142,7 +28146,11 @@
           <t>Net income (loss) .�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.� $</t>
         </is>
       </c>
-      <c r="D475" t="inlineStr"/>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E475" t="inlineStr">
         <is>
           <t>-</t>
@@ -29161,7 +29169,11 @@
           <t>Purchase of intangible assets �.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�</t>
         </is>
       </c>
-      <c r="D496" t="inlineStr"/>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E496" t="inlineStr">
         <is>
           <t>-</t>
@@ -31078,7 +31090,11 @@
           <t>Purchase of intangible assets �.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�.�</t>
         </is>
       </c>
-      <c r="D535" t="inlineStr"/>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E535" s="5" t="n">
         <v>-27.597</v>
       </c>
@@ -33048,7 +33064,11 @@
           <t>Purchase of intangible assets ��������������������������������������������������������</t>
         </is>
       </c>
-      <c r="D575" t="inlineStr"/>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E575" s="5" t="n">
         <v>-27.597</v>
       </c>
